--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104734_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104734_W31.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3231</v>
+        <v>6.1779</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3251</v>
+        <v>6.4774</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0019</v>
+        <v>-0.2995</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4655</v>
+        <v>4.4497</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4623</v>
+        <v>3.4506</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0033</v>
+        <v>0.999</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9061</v>
+        <v>5.8807</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6126</v>
+        <v>3.595</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2935</v>
+        <v>2.2857</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4405</v>
+        <v>-1.431</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1503</v>
+        <v>-0.1444</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.2902</v>
+        <v>-1.2866</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4608</v>
+        <v>0.4112</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5363</v>
+        <v>0.6454</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0755</v>
+        <v>-0.2342</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3906</v>
+        <v>3.5618</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2038</v>
+        <v>3.6676</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1868</v>
+        <v>-0.1059</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7228</v>
+        <v>3.7218</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8761</v>
+        <v>1.8779</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8468</v>
+        <v>1.8439</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6138</v>
+        <v>3.604</v>
       </c>
       <c r="K3" t="n">
-        <v>1.538</v>
+        <v>1.5341</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0758</v>
+        <v>2.0699</v>
       </c>
       <c r="M3" t="n">
-        <v>0.109</v>
+        <v>0.1178</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3381</v>
+        <v>0.3438</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.229</v>
+        <v>-0.226</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9184</v>
+        <v>1.0872</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1803</v>
+        <v>0.6571</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7381</v>
+        <v>0.4302</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7963</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7408</v>
+        <v>3.0838</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8129</v>
+        <v>4.2669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.928</v>
+        <v>-1.1832</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0142</v>
+        <v>1.8657</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2653</v>
+        <v>3.9035</v>
       </c>
       <c r="I4" t="n">
-        <v>0.749</v>
+        <v>-2.0377</v>
       </c>
       <c r="J4" t="n">
-        <v>1.279</v>
+        <v>3.0968</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2045</v>
+        <v>4.3782</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>-1.2814</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2648</v>
+        <v>-1.231</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9392</v>
+        <v>-0.4747</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6744</v>
+        <v>-0.7563</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9091</v>
+        <v>0.3774</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5338</v>
+        <v>1.0124</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3753</v>
+        <v>-0.635</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5456</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2577</v>
+        <v>3.0351</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1337</v>
+        <v>1.9585</v>
       </c>
       <c r="F5" t="n">
-        <v>1.124</v>
+        <v>1.0765</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1205</v>
+        <v>1.7969</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.2958</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5998</v>
+        <v>1.5011</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9299</v>
+        <v>2.1818</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5132</v>
+        <v>1.2443</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4167</v>
+        <v>0.9375</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8094</v>
+        <v>-0.3849</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0075</v>
+        <v>-0.9485</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8169</v>
+        <v>0.5636</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9087</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4325</v>
+        <v>0.6448</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1803</v>
+        <v>-0.2232</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2522</v>
+        <v>0.868</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9318</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7724</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.043</v>
+        <v>2.976</v>
       </c>
       <c r="E6" t="n">
-        <v>4.519</v>
+        <v>1.8349</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.476</v>
+        <v>1.141</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8694</v>
+        <v>1.122</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9085</v>
+        <v>0.5199</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0392</v>
+        <v>0.6021</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1099</v>
+        <v>1.9214</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3894</v>
+        <v>0.5064</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2796</v>
+        <v>1.415</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2405</v>
+        <v>-0.7993</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4809</v>
+        <v>0.0135</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.8129</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6816</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3327</v>
+        <v>1.1499</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2497</v>
+        <v>0.894</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9171</v>
+        <v>0.2559</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1594</v>
+        <v>0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7025</v>
+        <v>2.5923</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3627</v>
+        <v>1.8065</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3398</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8013</v>
+        <v>1.0129</v>
       </c>
       <c r="H7" t="n">
-        <v>0.296</v>
+        <v>0.2618</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5052</v>
+        <v>0.7511</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1956</v>
+        <v>1.2703</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2503</v>
+        <v>1.1958</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9453</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3944</v>
+        <v>-0.2574</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9543</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5599</v>
+        <v>0.6766</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1359</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1359</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.311</v>
+        <v>0.7583</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8329</v>
+        <v>0.5362</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1438</v>
+        <v>0.2221</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5538</v>
+        <v>1.1844</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9201</v>
+        <v>1.2478</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3663</v>
+        <v>-0.0635</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.737</v>
+        <v>-1.7378</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6079</v>
+        <v>-1.6082</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1292</v>
+        <v>-0.1297</v>
       </c>
       <c r="J8" t="n">
-        <v>0.066</v>
+        <v>0.0508</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7362</v>
+        <v>-0.7454</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8022</v>
+        <v>0.7962</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.803</v>
+        <v>-1.7886</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8716</v>
+        <v>-0.8628</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9314</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2443</v>
+        <v>0.8814</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3979</v>
+        <v>0.7497</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1536</v>
+        <v>0.1317</v>
       </c>
       <c r="V8" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.332</v>
+        <v>0.3918</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0795</v>
+        <v>-0.0839</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4116</v>
+        <v>0.4757</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1773</v>
+        <v>0.178</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1383</v>
+        <v>-0.1379</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3156</v>
+        <v>0.3159</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1427</v>
+        <v>0.1435</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3156</v>
+        <v>0.3159</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0278</v>
+        <v>0.0349</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0694</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0416</v>
+        <v>0.1046</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3263</v>
+        <v>-0.2268</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0596</v>
+        <v>-1.8204</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7333</v>
+        <v>1.5936</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1148</v>
+        <v>-3.1165</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2525</v>
+        <v>0.2502</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3673</v>
+        <v>-3.3667</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3777</v>
+        <v>-2.3881</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7033</v>
+        <v>0.696</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.081</v>
+        <v>-3.0841</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7371</v>
+        <v>-0.7284</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4508</v>
+        <v>-0.4458</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2863</v>
+        <v>-0.2826</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6973</v>
+        <v>0.8002</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1828</v>
+        <v>0.0717</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8801</v>
+        <v>0.7286</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6317</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>1.21</v>
+        <v>1.0376</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8417</v>
+        <v>-1.6087</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1454</v>
+        <v>-2.1402</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7326</v>
+        <v>-1.7293</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4128</v>
+        <v>-0.4109</v>
       </c>
       <c r="J11" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0949</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.305</v>
+        <v>-0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4041</v>
+        <v>0.4019</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2444</v>
+        <v>-2.2351</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4276</v>
+        <v>-1.4223</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8169</v>
+        <v>-0.8129</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.31</v>
+        <v>0.3611</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1109</v>
+        <v>0.9427</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.5816</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.792</v>
+        <v>-0.6409</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1215</v>
+        <v>-0.0037</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6704</v>
+        <v>-0.6372</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.7419</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1555</v>
+        <v>-0.1551</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7607</v>
+        <v>-0.7592</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2758</v>
+        <v>-0.1266</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1388</v>
+        <v>-0.021</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.137</v>
+        <v>-0.1057</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7622</v>
+        <v>-1.0382</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9225</v>
+        <v>-2.5518</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1603</v>
+        <v>1.5135</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.9598</v>
+        <v>-1.9569</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8986</v>
+        <v>-0.8963</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0612</v>
+        <v>-1.0606</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2285</v>
+        <v>-2.231</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5778</v>
+        <v>-1.5793</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2686</v>
+        <v>0.2741</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.248</v>
+        <v>-0.2446</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5187</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7112000000000001</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.3207</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0171</v>
+        <v>0.3289</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.8313</v>
+        <v>20.5261</v>
       </c>
       <c r="E14" t="n">
-        <v>17.3042</v>
+        <v>17.8374</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5275</v>
+        <v>2.688099999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>4.470600000000001</v>
+        <v>4.453699999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>6.048499999999999</v>
+        <v>6.032899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5778</v>
+        <v>-1.5793</v>
       </c>
       <c r="J14" t="n">
-        <v>13.6451</v>
+        <v>13.5333</v>
       </c>
       <c r="K14" t="n">
-        <v>11.5713</v>
+        <v>11.4974</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0738</v>
+        <v>2.0359</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.1745</v>
+        <v>-9.079499999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.5227</v>
+        <v>-5.4646</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.651600000000001</v>
+        <v>-3.6152</v>
       </c>
       <c r="P14" t="n">
-        <v>4.543699999999999</v>
+        <v>4.552699999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.9514</v>
+        <v>-7.967300000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4951</v>
+        <v>12.5197</v>
       </c>
       <c r="S14" t="n">
-        <v>5.6797</v>
+        <v>6.388000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>4.198600000000002</v>
+        <v>4.874600000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4809</v>
+        <v>1.5135</v>
       </c>
       <c r="V14" t="n">
-        <v>5.1375</v>
+        <v>5.132000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>7.411999999999999</v>
+        <v>7.3972</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2745</v>
+        <v>-2.2653</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5878</v>
+        <v>1.7032</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9348</v>
+        <v>1.6828</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3471</v>
+        <v>0.0205</v>
       </c>
       <c r="G15" t="n">
-        <v>1.529</v>
+        <v>0.917</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6635</v>
+        <v>1.419</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1345</v>
+        <v>-0.502</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9788</v>
+        <v>1.661</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9415</v>
+        <v>1.937</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>-0.276</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4498</v>
+        <v>-0.7441</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.278</v>
+        <v>-0.518</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1718</v>
+        <v>-0.226</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4544</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5131</v>
+        <v>-0.8966</v>
       </c>
       <c r="T15" t="n">
-        <v>1.092</v>
+        <v>-0.523</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5788</v>
+        <v>-0.3736</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9276</v>
+        <v>1.0251</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1097</v>
+        <v>1.332</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1822</v>
+        <v>-0.3069</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9196</v>
+        <v>1.528</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4216</v>
+        <v>1.6603</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.502</v>
+        <v>-0.1323</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6746</v>
+        <v>1.971</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9476</v>
+        <v>1.9338</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.273</v>
+        <v>0.0372</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.755</v>
+        <v>-0.443</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.526</v>
+        <v>-0.2734</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.229</v>
+        <v>-0.1695</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1359</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1359</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6736</v>
+        <v>-0.0476</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1105</v>
+        <v>0.4991</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5631</v>
+        <v>-0.5468</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5456</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5456</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9016</v>
+        <v>0.7179</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0618</v>
+        <v>-0.0629</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9634</v>
+        <v>0.7809</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4018</v>
+        <v>0.4043</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0256</v>
+        <v>-0.0233</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4274</v>
+        <v>0.4276</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1464</v>
+        <v>0.1462</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2554</v>
+        <v>0.2581</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0601</v>
+        <v>-0.0578</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3156</v>
+        <v>0.3159</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0454</v>
+        <v>-0.1416</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2082</v>
+        <v>-0.2091</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2536</v>
+        <v>0.0675</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.484</v>
       </c>
       <c r="E18" t="n">
-        <v>0.042</v>
+        <v>0.0383</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5361</v>
+        <v>0.4457</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9745</v>
+        <v>-0.9737</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3434</v>
+        <v>-0.3419</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6311</v>
+        <v>-0.6317</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7716</v>
+        <v>-0.7724</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2029</v>
+        <v>-0.2012</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3607</v>
+        <v>-0.3592</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0069</v>
+        <v>-0.0871</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2776</v>
+        <v>-0.2788</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2846</v>
+        <v>0.1917</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4702</v>
+        <v>-0.3184</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0097</v>
+        <v>2.3859</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.48</v>
+        <v>-2.7043</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7312</v>
+        <v>2.282</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.656</v>
+        <v>-2.1402</v>
       </c>
       <c r="I19" t="n">
-        <v>3.3873</v>
+        <v>4.4222</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0348</v>
+        <v>3.9589</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2074</v>
+        <v>-0.1142</v>
       </c>
       <c r="L19" t="n">
-        <v>2.8274</v>
+        <v>4.073</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3035</v>
+        <v>-1.6769</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8634</v>
+        <v>-2.026</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5599</v>
+        <v>0.3492</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9087</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9087</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9277</v>
+        <v>-1.0557</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.025</v>
+        <v>-0.4348</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.6209</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1825</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1825</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9726</v>
+        <v>-0.4189</v>
       </c>
       <c r="E20" t="n">
-        <v>1.816</v>
+        <v>2.8825</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7886</v>
+        <v>-3.3013</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2827</v>
+        <v>1.7391</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1451</v>
+        <v>-1.6468</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4278</v>
+        <v>3.3859</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9741</v>
+        <v>3.0292</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1089</v>
+        <v>0.2068</v>
       </c>
       <c r="L20" t="n">
-        <v>4.083</v>
+        <v>2.8223</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6914</v>
+        <v>-1.2901</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0362</v>
+        <v>-1.8536</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3449</v>
+        <v>0.5636</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4544</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7097</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0221</v>
+        <v>-0.1467</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6875</v>
+        <v>-0.7428</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0913</v>
+        <v>-2.1789</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0913</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5697</v>
+        <v>-1.8686</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8126</v>
+        <v>-0.4153</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3823</v>
+        <v>-1.4533</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6025</v>
+        <v>-1.9533</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4906</v>
+        <v>-1.8415</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1118</v>
+        <v>-0.1117</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7274</v>
+        <v>-0.5775</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9565</v>
+        <v>-0.376</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7709</v>
+        <v>-0.2015</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.125</v>
+        <v>-1.3758</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4659</v>
+        <v>-1.4656</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6591</v>
+        <v>0.0898</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6816</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4544</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3993</v>
+        <v>-0.1626</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6755</v>
+        <v>0.0531</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0748</v>
+        <v>-0.2157</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0913</v>
+        <v>0.7025</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5456</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6369</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5164</v>
+        <v>-2.0001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1382</v>
+        <v>1.087</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6545</v>
+        <v>-3.0871</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2673</v>
+        <v>0.6027</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0429</v>
+        <v>0.491</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2244</v>
+        <v>0.1117</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8019</v>
+        <v>1.7179</v>
       </c>
       <c r="K22" t="n">
-        <v>3.019</v>
+        <v>0.9513</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7829</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5346</v>
+        <v>-1.1152</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.9761</v>
+        <v>-0.4603</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5585</v>
+        <v>-0.6549</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8175</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2619</v>
+        <v>-0.8305</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2332</v>
+        <v>-0.0375</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0287</v>
+        <v>-0.7929</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7043</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.1587</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5456</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5575</v>
+        <v>-2.6406</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9941</v>
+        <v>-0.0054</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5634</v>
+        <v>-2.6352</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9587</v>
+        <v>1.2659</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8468</v>
+        <v>1.0375</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1118</v>
+        <v>0.2285</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5726</v>
+        <v>3.7877</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3742</v>
+        <v>3.0057</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1984</v>
+        <v>0.782</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3861</v>
+        <v>-2.5218</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4727</v>
+        <v>-1.9683</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0866</v>
+        <v>-0.5535</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4544</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6816</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8495</v>
+        <v>-0.3798</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5363</v>
+        <v>-0.3558</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3132</v>
+        <v>-0.024</v>
       </c>
       <c r="V23" t="n">
-        <v>0.705</v>
+        <v>-1.7057</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2507</v>
+        <v>-1.1609</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2463</v>
+        <v>-3.337</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7765</v>
+        <v>-1.9143</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4698</v>
+        <v>-1.4227</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3042</v>
+        <v>0.3041</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4388</v>
+        <v>-0.4393</v>
       </c>
       <c r="I24" t="n">
-        <v>0.743</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7447</v>
+        <v>1.7352</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1849</v>
+        <v>0.1789</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5598</v>
+        <v>1.5563</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4405</v>
+        <v>-1.431</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6237</v>
+        <v>-0.6182</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8169</v>
+        <v>-0.8129</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0398</v>
+        <v>-0.0476</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1134</v>
+        <v>-0.2349</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1532</v>
+        <v>0.1873</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.021</v>
+        <v>-5.2711</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9377</v>
+        <v>-4.3578</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0833</v>
+        <v>-0.9133</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.325</v>
+        <v>-4.3223</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3066</v>
+        <v>-0.3047</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.0184</v>
+        <v>-4.0176</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.8995</v>
+        <v>-2.9057</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1443</v>
+        <v>0.1411</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.0438</v>
+        <v>-3.0469</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4255</v>
+        <v>-1.4166</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4508</v>
+        <v>-0.4458</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9746</v>
+        <v>-0.9708</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0823</v>
+        <v>-0.3357</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9023</v>
+        <v>-0.3139</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.18</v>
+        <v>-0.0218</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.4727</v>
+        <v>-7.115</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.6203</v>
+        <v>-5.3411</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8524</v>
+        <v>-1.7739</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.2508</v>
+        <v>-6.2476</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.9047</v>
+        <v>-3.903</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.3461</v>
+        <v>-2.3446</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.6647</v>
+        <v>-4.6718</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.4471</v>
+        <v>-2.4519</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.2176</v>
+        <v>-2.22</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.5861</v>
+        <v>-1.5758</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.4577</v>
+        <v>-1.4511</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1285</v>
+        <v>-0.1246</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6191</v>
+        <v>-0.0267</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1803</v>
+        <v>0.4689</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5612</v>
+        <v>-0.4956</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-19.8313</v>
+        <v>-19.0395</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.527399999999999</v>
+        <v>-2.688300000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-17.3041</v>
+        <v>-16.3509</v>
       </c>
       <c r="G27" t="n">
-        <v>-4.4707</v>
+        <v>-4.453799999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.0484</v>
+        <v>-6.0329</v>
       </c>
       <c r="I27" t="n">
-        <v>1.577800000000002</v>
+        <v>1.579400000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>9.174300000000002</v>
+        <v>9.079699999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>5.522900000000001</v>
+        <v>5.464199999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>3.651400000000001</v>
+        <v>3.615100000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-13.645</v>
+        <v>-13.5334</v>
       </c>
       <c r="N27" t="n">
-        <v>-11.5713</v>
+        <v>-11.4973</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.0736</v>
+        <v>-2.0358</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.544</v>
+        <v>-4.552699999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.4951</v>
+        <v>-12.52</v>
       </c>
       <c r="R27" t="n">
-        <v>7.951699999999999</v>
+        <v>7.967300000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.6797</v>
+        <v>-4.9011</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.4808</v>
+        <v>-1.5134</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.1986</v>
+        <v>-3.3876</v>
       </c>
       <c r="V27" t="n">
-        <v>-5.137599999999999</v>
+        <v>-5.132</v>
       </c>
       <c r="W27" t="n">
-        <v>2.2745</v>
+        <v>2.2652</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.412000000000001</v>
+        <v>-7.3971</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104734_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104734_W31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-2.2653</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104734_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-7.3971</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
